--- a/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/180-Day Execution Plan.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/180-Day Execution Plan.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="228">
   <si>
     <t xml:space="preserve">Plan de ejecución de 180 días (26 semanas) — Proyecto A con vía B3 en validación</t>
   </si>
@@ -248,6 +248,36 @@
     <t xml:space="preserve">Condición C2</t>
   </si>
   <si>
+    <t xml:space="preserve">0.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arnaldo: consentimiento escrito al uso de su nombre/firma, autorización de su empleador, firmas escaneadas y retrato opcional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promotor + abogado cubano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consentimiento firmado + materiales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin consentimiento → usar reserva FOLIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2 Marca y producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brief creativo a 3 estudios de packaging premium y selección</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 presupuestos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encargo ≤ 15 k€</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.7</t>
   </si>
   <si>
@@ -362,10 +392,7 @@
     <t xml:space="preserve">2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">F2 Marca y producto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Encargar informe de registrabilidad FOLIO / LUMBRE / VELADA (EUIPO, OEPM, OCPI)</t>
+    <t xml:space="preserve">Encargar informe de registrabilidad ARNALDO (+ apellido y firma) y reservas FOLIO / LUMBRE (EUIPO, OEPM, OCPI)</t>
   </si>
   <si>
     <t xml:space="preserve">Agente de marcas</t>
@@ -1204,7 +1231,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AM39"/>
+  <dimension ref="A1:AM41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2238,20 +2265,20 @@
         <v>76</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" s="6" t="n">
         <f aca="false">F11+G11-1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0</v>
@@ -2260,25 +2287,25 @@
         <v>52</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="N11" s="9" t="n">
         <f aca="false">IF(AND(1&gt;=$F11,1&lt;=$H11),1,"")</f>
         <v>1</v>
       </c>
-      <c r="O11" s="9" t="str">
+      <c r="O11" s="9" t="n">
         <f aca="false">IF(AND(2&gt;=$F11,2&lt;=$H11),1,"")</f>
-        <v/>
-      </c>
-      <c r="P11" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="P11" s="9" t="n">
         <f aca="false">IF(AND(3&gt;=$F11,3&lt;=$H11),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Q11" s="9" t="str">
         <f aca="false">IF(AND(4&gt;=$F11,4&lt;=$H11),1,"")</f>
@@ -2373,66 +2400,66 @@
         <v/>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H12" s="6" t="n">
         <f aca="false">F12+G12-1</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>61</v>
+        <v>84</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="N12" s="9" t="str">
         <f aca="false">IF(AND(1&gt;=$F12,1&lt;=$H12),1,"")</f>
         <v/>
       </c>
-      <c r="O12" s="9" t="str">
+      <c r="O12" s="9" t="n">
         <f aca="false">IF(AND(2&gt;=$F12,2&lt;=$H12),1,"")</f>
-        <v/>
-      </c>
-      <c r="P12" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="P12" s="9" t="n">
         <f aca="false">IF(AND(3&gt;=$F12,3&lt;=$H12),1,"")</f>
-        <v/>
-      </c>
-      <c r="Q12" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="9" t="n">
         <f aca="false">IF(AND(4&gt;=$F12,4&lt;=$H12),1,"")</f>
-        <v/>
-      </c>
-      <c r="R12" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="R12" s="9" t="n">
         <f aca="false">IF(AND(5&gt;=$F12,5&lt;=$H12),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="S12" s="9" t="str">
         <f aca="false">IF(AND(6&gt;=$F12,6&lt;=$H12),1,"")</f>
@@ -2454,9 +2481,9 @@
         <f aca="false">IF(AND(10&gt;=$F12,10&lt;=$H12),1,"")</f>
         <v/>
       </c>
-      <c r="X12" s="9" t="n">
+      <c r="X12" s="9" t="str">
         <f aca="false">IF(AND(11&gt;=$F12,11&lt;=$H12),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Y12" s="9" t="str">
         <f aca="false">IF(AND(12&gt;=$F12,12&lt;=$H12),1,"")</f>
@@ -2521,64 +2548,64 @@
     </row>
     <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>86</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H13" s="6" t="n">
         <f aca="false">F13+G13-1</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N13" s="9" t="str">
+        <v>88</v>
+      </c>
+      <c r="N13" s="9" t="n">
         <f aca="false">IF(AND(1&gt;=$F13,1&lt;=$H13),1,"")</f>
-        <v/>
-      </c>
-      <c r="O13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="9" t="str">
         <f aca="false">IF(AND(2&gt;=$F13,2&lt;=$H13),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="P13" s="9" t="n">
+        <v/>
+      </c>
+      <c r="P13" s="9" t="str">
         <f aca="false">IF(AND(3&gt;=$F13,3&lt;=$H13),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="9" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="9" t="str">
         <f aca="false">IF(AND(4&gt;=$F13,4&lt;=$H13),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="R13" s="9" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="9" t="str">
         <f aca="false">IF(AND(5&gt;=$F13,5&lt;=$H13),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="S13" s="9" t="str">
         <f aca="false">IF(AND(6&gt;=$F13,6&lt;=$H13),1,"")</f>
@@ -2667,60 +2694,60 @@
     </row>
     <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="F14" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" s="6" t="n">
         <f aca="false">F14+G14-1</f>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>49</v>
+        <v>93</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="N14" s="9" t="str">
         <f aca="false">IF(AND(1&gt;=$F14,1&lt;=$H14),1,"")</f>
         <v/>
       </c>
-      <c r="O14" s="9" t="n">
+      <c r="O14" s="9" t="str">
         <f aca="false">IF(AND(2&gt;=$F14,2&lt;=$H14),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="P14" s="9" t="n">
+        <v/>
+      </c>
+      <c r="P14" s="9" t="str">
         <f aca="false">IF(AND(3&gt;=$F14,3&lt;=$H14),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="Q14" s="9" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="9" t="str">
         <f aca="false">IF(AND(4&gt;=$F14,4&lt;=$H14),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="R14" s="9" t="str">
         <f aca="false">IF(AND(5&gt;=$F14,5&lt;=$H14),1,"")</f>
@@ -2746,9 +2773,9 @@
         <f aca="false">IF(AND(10&gt;=$F14,10&lt;=$H14),1,"")</f>
         <v/>
       </c>
-      <c r="X14" s="9" t="str">
+      <c r="X14" s="9" t="n">
         <f aca="false">IF(AND(11&gt;=$F14,11&lt;=$H14),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y14" s="9" t="str">
         <f aca="false">IF(AND(12&gt;=$F14,12&lt;=$H14),1,"")</f>
@@ -2811,43 +2838,43 @@
         <v/>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="6" t="n">
         <f aca="false">F15+G15-1</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>99</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="M15" s="8" t="s">
         <v>49</v>
@@ -2864,13 +2891,13 @@
         <f aca="false">IF(AND(3&gt;=$F15,3&lt;=$H15),1,"")</f>
         <v>1</v>
       </c>
-      <c r="Q15" s="9" t="str">
+      <c r="Q15" s="9" t="n">
         <f aca="false">IF(AND(4&gt;=$F15,4&lt;=$H15),1,"")</f>
-        <v/>
-      </c>
-      <c r="R15" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="R15" s="9" t="n">
         <f aca="false">IF(AND(5&gt;=$F15,5&lt;=$H15),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="S15" s="9" t="str">
         <f aca="false">IF(AND(6&gt;=$F15,6&lt;=$H15),1,"")</f>
@@ -2959,16 +2986,16 @@
     </row>
     <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>48</v>
@@ -2977,20 +3004,20 @@
         <v>2</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" s="6" t="n">
         <f aca="false">F16+G16-1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>48</v>
@@ -3006,13 +3033,13 @@
         <f aca="false">IF(AND(2&gt;=$F16,2&lt;=$H16),1,"")</f>
         <v>1</v>
       </c>
-      <c r="P16" s="9" t="str">
+      <c r="P16" s="9" t="n">
         <f aca="false">IF(AND(3&gt;=$F16,3&lt;=$H16),1,"")</f>
-        <v/>
-      </c>
-      <c r="Q16" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="9" t="n">
         <f aca="false">IF(AND(4&gt;=$F16,4&lt;=$H16),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="R16" s="9" t="str">
         <f aca="false">IF(AND(5&gt;=$F16,5&lt;=$H16),1,"")</f>
@@ -3103,43 +3130,43 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" s="6" t="n">
         <f aca="false">F17+G17-1</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="M17" s="8" t="s">
         <v>49</v>
@@ -3148,21 +3175,21 @@
         <f aca="false">IF(AND(1&gt;=$F17,1&lt;=$H17),1,"")</f>
         <v/>
       </c>
-      <c r="O17" s="9" t="str">
+      <c r="O17" s="9" t="n">
         <f aca="false">IF(AND(2&gt;=$F17,2&lt;=$H17),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P17" s="9" t="n">
         <f aca="false">IF(AND(3&gt;=$F17,3&lt;=$H17),1,"")</f>
         <v>1</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="9" t="str">
         <f aca="false">IF(AND(4&gt;=$F17,4&lt;=$H17),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="R17" s="9" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="9" t="str">
         <f aca="false">IF(AND(5&gt;=$F17,5&lt;=$H17),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="S17" s="9" t="str">
         <f aca="false">IF(AND(6&gt;=$F17,6&lt;=$H17),1,"")</f>
@@ -3249,54 +3276,54 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" s="6" t="n">
         <f aca="false">F18+G18-1</f>
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="M18" s="10" t="s">
-        <v>61</v>
+      <c r="M18" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="N18" s="9" t="str">
         <f aca="false">IF(AND(1&gt;=$F18,1&lt;=$H18),1,"")</f>
         <v/>
       </c>
-      <c r="O18" s="9" t="str">
+      <c r="O18" s="9" t="n">
         <f aca="false">IF(AND(2&gt;=$F18,2&lt;=$H18),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P18" s="9" t="str">
         <f aca="false">IF(AND(3&gt;=$F18,3&lt;=$H18),1,"")</f>
@@ -3334,17 +3361,17 @@
         <f aca="false">IF(AND(11&gt;=$F18,11&lt;=$H18),1,"")</f>
         <v/>
       </c>
-      <c r="Y18" s="9" t="n">
+      <c r="Y18" s="9" t="str">
         <f aca="false">IF(AND(12&gt;=$F18,12&lt;=$H18),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="Z18" s="9" t="n">
+        <v/>
+      </c>
+      <c r="Z18" s="9" t="str">
         <f aca="false">IF(AND(13&gt;=$F18,13&lt;=$H18),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AA18" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AA18" s="9" t="str">
         <f aca="false">IF(AND(14&gt;=$F18,14&lt;=$H18),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AB18" s="9" t="str">
         <f aca="false">IF(AND(15&gt;=$F18,15&lt;=$H18),1,"")</f>
@@ -3397,41 +3424,41 @@
     </row>
     <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>114</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H19" s="6" t="n">
         <f aca="false">F19+G19-1</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M19" s="8" t="s">
         <v>49</v>
@@ -3456,9 +3483,9 @@
         <f aca="false">IF(AND(5&gt;=$F19,5&lt;=$H19),1,"")</f>
         <v>1</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="S19" s="9" t="str">
         <f aca="false">IF(AND(6&gt;=$F19,6&lt;=$H19),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T19" s="9" t="str">
         <f aca="false">IF(AND(7&gt;=$F19,7&lt;=$H19),1,"")</f>
@@ -3543,35 +3570,35 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>112</v>
-      </c>
       <c r="F20" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" s="6" t="n">
         <f aca="false">F20+G20-1</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>121</v>
@@ -3579,8 +3606,8 @@
       <c r="L20" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="M20" s="8" t="s">
-        <v>122</v>
+      <c r="M20" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="N20" s="9" t="str">
         <f aca="false">IF(AND(1&gt;=$F20,1&lt;=$H20),1,"")</f>
@@ -3610,9 +3637,9 @@
         <f aca="false">IF(AND(7&gt;=$F20,7&lt;=$H20),1,"")</f>
         <v/>
       </c>
-      <c r="U20" s="9" t="n">
+      <c r="U20" s="9" t="str">
         <f aca="false">IF(AND(8&gt;=$F20,8&lt;=$H20),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="V20" s="9" t="str">
         <f aca="false">IF(AND(9&gt;=$F20,9&lt;=$H20),1,"")</f>
@@ -3626,17 +3653,17 @@
         <f aca="false">IF(AND(11&gt;=$F20,11&lt;=$H20),1,"")</f>
         <v/>
       </c>
-      <c r="Y20" s="9" t="str">
+      <c r="Y20" s="9" t="n">
         <f aca="false">IF(AND(12&gt;=$F20,12&lt;=$H20),1,"")</f>
-        <v/>
-      </c>
-      <c r="Z20" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="9" t="n">
         <f aca="false">IF(AND(13&gt;=$F20,13&lt;=$H20),1,"")</f>
-        <v/>
-      </c>
-      <c r="AA20" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="9" t="n">
         <f aca="false">IF(AND(14&gt;=$F20,14&lt;=$H20),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AB20" s="9" t="str">
         <f aca="false">IF(AND(15&gt;=$F20,15&lt;=$H20),1,"")</f>
@@ -3687,34 +3714,34 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="F21" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>4</v>
       </c>
       <c r="H21" s="6" t="n">
         <f aca="false">F21+G21-1</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>46</v>
@@ -3725,8 +3752,8 @@
       <c r="L21" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="M21" s="10" t="s">
-        <v>61</v>
+      <c r="M21" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="N21" s="9" t="str">
         <f aca="false">IF(AND(1&gt;=$F21,1&lt;=$H21),1,"")</f>
@@ -3736,21 +3763,21 @@
         <f aca="false">IF(AND(2&gt;=$F21,2&lt;=$H21),1,"")</f>
         <v/>
       </c>
-      <c r="P21" s="9" t="str">
+      <c r="P21" s="9" t="n">
         <f aca="false">IF(AND(3&gt;=$F21,3&lt;=$H21),1,"")</f>
-        <v/>
-      </c>
-      <c r="Q21" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="9" t="n">
         <f aca="false">IF(AND(4&gt;=$F21,4&lt;=$H21),1,"")</f>
-        <v/>
-      </c>
-      <c r="R21" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="R21" s="9" t="n">
         <f aca="false">IF(AND(5&gt;=$F21,5&lt;=$H21),1,"")</f>
-        <v/>
-      </c>
-      <c r="S21" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="S21" s="9" t="n">
         <f aca="false">IF(AND(6&gt;=$F21,6&lt;=$H21),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T21" s="9" t="str">
         <f aca="false">IF(AND(7&gt;=$F21,7&lt;=$H21),1,"")</f>
@@ -3760,21 +3787,21 @@
         <f aca="false">IF(AND(8&gt;=$F21,8&lt;=$H21),1,"")</f>
         <v/>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="9" t="str">
         <f aca="false">IF(AND(9&gt;=$F21,9&lt;=$H21),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="W21" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W21" s="9" t="str">
         <f aca="false">IF(AND(10&gt;=$F21,10&lt;=$H21),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="X21" s="9" t="n">
+        <v/>
+      </c>
+      <c r="X21" s="9" t="str">
         <f aca="false">IF(AND(11&gt;=$F21,11&lt;=$H21),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="Y21" s="9" t="n">
+        <v/>
+      </c>
+      <c r="Y21" s="9" t="str">
         <f aca="false">IF(AND(12&gt;=$F21,12&lt;=$H21),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z21" s="9" t="str">
         <f aca="false">IF(AND(13&gt;=$F21,13&lt;=$H21),1,"")</f>
@@ -3838,41 +3865,41 @@
         <v>128</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H22" s="6" t="n">
         <f aca="false">F22+G22-1</f>
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K22" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M22" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>61</v>
       </c>
       <c r="N22" s="9" t="str">
         <f aca="false">IF(AND(1&gt;=$F22,1&lt;=$H22),1,"")</f>
@@ -3902,9 +3929,9 @@
         <f aca="false">IF(AND(7&gt;=$F22,7&lt;=$H22),1,"")</f>
         <v/>
       </c>
-      <c r="U22" s="9" t="str">
+      <c r="U22" s="9" t="n">
         <f aca="false">IF(AND(8&gt;=$F22,8&lt;=$H22),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V22" s="9" t="str">
         <f aca="false">IF(AND(9&gt;=$F22,9&lt;=$H22),1,"")</f>
@@ -3922,29 +3949,29 @@
         <f aca="false">IF(AND(12&gt;=$F22,12&lt;=$H22),1,"")</f>
         <v/>
       </c>
-      <c r="Z22" s="9" t="n">
+      <c r="Z22" s="9" t="str">
         <f aca="false">IF(AND(13&gt;=$F22,13&lt;=$H22),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AA22" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AA22" s="9" t="str">
         <f aca="false">IF(AND(14&gt;=$F22,14&lt;=$H22),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AB22" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AB22" s="9" t="str">
         <f aca="false">IF(AND(15&gt;=$F22,15&lt;=$H22),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AC22" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AC22" s="9" t="str">
         <f aca="false">IF(AND(16&gt;=$F22,16&lt;=$H22),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AD22" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AD22" s="9" t="str">
         <f aca="false">IF(AND(17&gt;=$F22,17&lt;=$H22),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AE22" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AE22" s="9" t="str">
         <f aca="false">IF(AND(18&gt;=$F22,18&lt;=$H22),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AF22" s="9" t="str">
         <f aca="false">IF(AND(19&gt;=$F22,19&lt;=$H22),1,"")</f>
@@ -3981,44 +4008,44 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="E23" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>4</v>
       </c>
       <c r="H23" s="6" t="n">
         <f aca="false">F23+G23-1</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="K23" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="L23" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="M23" s="8" t="s">
-        <v>122</v>
+      <c r="M23" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="N23" s="9" t="str">
         <f aca="false">IF(AND(1&gt;=$F23,1&lt;=$H23),1,"")</f>
@@ -4052,9 +4079,9 @@
         <f aca="false">IF(AND(8&gt;=$F23,8&lt;=$H23),1,"")</f>
         <v/>
       </c>
-      <c r="V23" s="9" t="str">
+      <c r="V23" s="9" t="n">
         <f aca="false">IF(AND(9&gt;=$F23,9&lt;=$H23),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="W23" s="9" t="n">
         <f aca="false">IF(AND(10&gt;=$F23,10&lt;=$H23),1,"")</f>
@@ -4068,9 +4095,9 @@
         <f aca="false">IF(AND(12&gt;=$F23,12&lt;=$H23),1,"")</f>
         <v>1</v>
       </c>
-      <c r="Z23" s="9" t="n">
+      <c r="Z23" s="9" t="str">
         <f aca="false">IF(AND(13&gt;=$F23,13&lt;=$H23),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AA23" s="9" t="str">
         <f aca="false">IF(AND(14&gt;=$F23,14&lt;=$H23),1,"")</f>
@@ -4125,43 +4152,43 @@
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="E24" s="4" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H24" s="6" t="n">
         <f aca="false">F24+G24-1</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>52</v>
       </c>
       <c r="K24" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="L24" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>142</v>
       </c>
       <c r="M24" s="10" t="s">
         <v>61</v>
@@ -4210,9 +4237,9 @@
         <f aca="false">IF(AND(11&gt;=$F24,11&lt;=$H24),1,"")</f>
         <v/>
       </c>
-      <c r="Y24" s="9" t="n">
+      <c r="Y24" s="9" t="str">
         <f aca="false">IF(AND(12&gt;=$F24,12&lt;=$H24),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z24" s="9" t="n">
         <f aca="false">IF(AND(13&gt;=$F24,13&lt;=$H24),1,"")</f>
@@ -4222,21 +4249,21 @@
         <f aca="false">IF(AND(14&gt;=$F24,14&lt;=$H24),1,"")</f>
         <v>1</v>
       </c>
-      <c r="AB24" s="9" t="str">
+      <c r="AB24" s="9" t="n">
         <f aca="false">IF(AND(15&gt;=$F24,15&lt;=$H24),1,"")</f>
-        <v/>
-      </c>
-      <c r="AC24" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="9" t="n">
         <f aca="false">IF(AND(16&gt;=$F24,16&lt;=$H24),1,"")</f>
-        <v/>
-      </c>
-      <c r="AD24" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="9" t="n">
         <f aca="false">IF(AND(17&gt;=$F24,17&lt;=$H24),1,"")</f>
-        <v/>
-      </c>
-      <c r="AE24" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AE24" s="9" t="n">
         <f aca="false">IF(AND(18&gt;=$F24,18&lt;=$H24),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF24" s="9" t="str">
         <f aca="false">IF(AND(19&gt;=$F24,19&lt;=$H24),1,"")</f>
@@ -4271,46 +4298,46 @@
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="E25" s="4" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>4</v>
       </c>
       <c r="H25" s="6" t="n">
         <f aca="false">F25+G25-1</f>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="K25" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="L25" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>61</v>
+      <c r="M25" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="N25" s="9" t="str">
         <f aca="false">IF(AND(1&gt;=$F25,1&lt;=$H25),1,"")</f>
@@ -4348,41 +4375,41 @@
         <f aca="false">IF(AND(9&gt;=$F25,9&lt;=$H25),1,"")</f>
         <v/>
       </c>
-      <c r="W25" s="9" t="str">
+      <c r="W25" s="9" t="n">
         <f aca="false">IF(AND(10&gt;=$F25,10&lt;=$H25),1,"")</f>
-        <v/>
-      </c>
-      <c r="X25" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="X25" s="9" t="n">
         <f aca="false">IF(AND(11&gt;=$F25,11&lt;=$H25),1,"")</f>
-        <v/>
-      </c>
-      <c r="Y25" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="9" t="n">
         <f aca="false">IF(AND(12&gt;=$F25,12&lt;=$H25),1,"")</f>
-        <v/>
-      </c>
-      <c r="Z25" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="9" t="n">
         <f aca="false">IF(AND(13&gt;=$F25,13&lt;=$H25),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA25" s="9" t="str">
         <f aca="false">IF(AND(14&gt;=$F25,14&lt;=$H25),1,"")</f>
         <v/>
       </c>
-      <c r="AB25" s="9" t="n">
+      <c r="AB25" s="9" t="str">
         <f aca="false">IF(AND(15&gt;=$F25,15&lt;=$H25),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AC25" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AC25" s="9" t="str">
         <f aca="false">IF(AND(16&gt;=$F25,16&lt;=$H25),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AD25" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AD25" s="9" t="str">
         <f aca="false">IF(AND(17&gt;=$F25,17&lt;=$H25),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AE25" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AE25" s="9" t="str">
         <f aca="false">IF(AND(18&gt;=$F25,18&lt;=$H25),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AF25" s="9" t="str">
         <f aca="false">IF(AND(19&gt;=$F25,19&lt;=$H25),1,"")</f>
@@ -4419,32 +4446,32 @@
     </row>
     <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>139</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>149</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H26" s="6" t="n">
         <f aca="false">F26+G26-1</f>
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>52</v>
@@ -4453,7 +4480,7 @@
         <v>150</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="M26" s="10" t="s">
         <v>61</v>
@@ -4502,17 +4529,17 @@
         <f aca="false">IF(AND(11&gt;=$F26,11&lt;=$H26),1,"")</f>
         <v/>
       </c>
-      <c r="Y26" s="9" t="str">
+      <c r="Y26" s="9" t="n">
         <f aca="false">IF(AND(12&gt;=$F26,12&lt;=$H26),1,"")</f>
-        <v/>
-      </c>
-      <c r="Z26" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="9" t="n">
         <f aca="false">IF(AND(13&gt;=$F26,13&lt;=$H26),1,"")</f>
-        <v/>
-      </c>
-      <c r="AA26" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="9" t="n">
         <f aca="false">IF(AND(14&gt;=$F26,14&lt;=$H26),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AB26" s="9" t="str">
         <f aca="false">IF(AND(15&gt;=$F26,15&lt;=$H26),1,"")</f>
@@ -4530,21 +4557,21 @@
         <f aca="false">IF(AND(18&gt;=$F26,18&lt;=$H26),1,"")</f>
         <v/>
       </c>
-      <c r="AF26" s="9" t="n">
+      <c r="AF26" s="9" t="str">
         <f aca="false">IF(AND(19&gt;=$F26,19&lt;=$H26),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AG26" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AG26" s="9" t="str">
         <f aca="false">IF(AND(20&gt;=$F26,20&lt;=$H26),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AH26" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AH26" s="9" t="str">
         <f aca="false">IF(AND(21&gt;=$F26,21&lt;=$H26),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AI26" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AI26" s="9" t="str">
         <f aca="false">IF(AND(22&gt;=$F26,22&lt;=$H26),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ26" s="9" t="str">
         <f aca="false">IF(AND(23&gt;=$F26,23&lt;=$H26),1,"")</f>
@@ -4565,41 +4592,41 @@
     </row>
     <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>153</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>15</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="6" t="n">
         <f aca="false">F27+G27-1</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>48</v>
+        <v>156</v>
       </c>
       <c r="M27" s="10" t="s">
         <v>61</v>
@@ -4672,9 +4699,9 @@
         <f aca="false">IF(AND(17&gt;=$F27,17&lt;=$H27),1,"")</f>
         <v>1</v>
       </c>
-      <c r="AE27" s="9" t="str">
+      <c r="AE27" s="9" t="n">
         <f aca="false">IF(AND(18&gt;=$F27,18&lt;=$H27),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF27" s="9" t="str">
         <f aca="false">IF(AND(19&gt;=$F27,19&lt;=$H27),1,"")</f>
@@ -4711,38 +4738,38 @@
     </row>
     <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>157</v>
-      </c>
       <c r="F28" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>4</v>
       </c>
       <c r="H28" s="6" t="n">
         <f aca="false">F28+G28-1</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>48</v>
@@ -4818,9 +4845,9 @@
         <f aca="false">IF(AND(17&gt;=$F28,17&lt;=$H28),1,"")</f>
         <v/>
       </c>
-      <c r="AE28" s="9" t="n">
+      <c r="AE28" s="9" t="str">
         <f aca="false">IF(AND(18&gt;=$F28,18&lt;=$H28),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AF28" s="9" t="n">
         <f aca="false">IF(AND(19&gt;=$F28,19&lt;=$H28),1,"")</f>
@@ -4834,9 +4861,9 @@
         <f aca="false">IF(AND(21&gt;=$F28,21&lt;=$H28),1,"")</f>
         <v>1</v>
       </c>
-      <c r="AI28" s="9" t="str">
+      <c r="AI28" s="9" t="n">
         <f aca="false">IF(AND(22&gt;=$F28,22&lt;=$H28),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AJ28" s="9" t="str">
         <f aca="false">IF(AND(23&gt;=$F28,23&lt;=$H28),1,"")</f>
@@ -4857,38 +4884,38 @@
     </row>
     <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" s="6" t="n">
         <f aca="false">F29+G29-1</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>300</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>48</v>
@@ -4952,33 +4979,33 @@
         <f aca="false">IF(AND(14&gt;=$F29,14&lt;=$H29),1,"")</f>
         <v/>
       </c>
-      <c r="AB29" s="9" t="str">
+      <c r="AB29" s="9" t="n">
         <f aca="false">IF(AND(15&gt;=$F29,15&lt;=$H29),1,"")</f>
-        <v/>
-      </c>
-      <c r="AC29" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="9" t="n">
         <f aca="false">IF(AND(16&gt;=$F29,16&lt;=$H29),1,"")</f>
-        <v/>
-      </c>
-      <c r="AD29" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AD29" s="9" t="n">
         <f aca="false">IF(AND(17&gt;=$F29,17&lt;=$H29),1,"")</f>
-        <v/>
-      </c>
-      <c r="AE29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" s="9" t="str">
         <f aca="false">IF(AND(18&gt;=$F29,18&lt;=$H29),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AF29" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AF29" s="9" t="str">
         <f aca="false">IF(AND(19&gt;=$F29,19&lt;=$H29),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AG29" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AG29" s="9" t="str">
         <f aca="false">IF(AND(20&gt;=$F29,20&lt;=$H29),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AH29" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AH29" s="9" t="str">
         <f aca="false">IF(AND(21&gt;=$F29,21&lt;=$H29),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AI29" s="9" t="str">
         <f aca="false">IF(AND(22&gt;=$F29,22&lt;=$H29),1,"")</f>
@@ -5003,38 +5030,38 @@
     </row>
     <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="6" t="n">
         <f aca="false">F30+G30-1</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>46</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>48</v>
@@ -5110,13 +5137,13 @@
         <f aca="false">IF(AND(17&gt;=$F30,17&lt;=$H30),1,"")</f>
         <v/>
       </c>
-      <c r="AE30" s="9" t="str">
+      <c r="AE30" s="9" t="n">
         <f aca="false">IF(AND(18&gt;=$F30,18&lt;=$H30),1,"")</f>
-        <v/>
-      </c>
-      <c r="AF30" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="9" t="n">
         <f aca="false">IF(AND(19&gt;=$F30,19&lt;=$H30),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AG30" s="9" t="n">
         <f aca="false">IF(AND(20&gt;=$F30,20&lt;=$H30),1,"")</f>
@@ -5126,9 +5153,9 @@
         <f aca="false">IF(AND(21&gt;=$F30,21&lt;=$H30),1,"")</f>
         <v>1</v>
       </c>
-      <c r="AI30" s="9" t="n">
+      <c r="AI30" s="9" t="str">
         <f aca="false">IF(AND(22&gt;=$F30,22&lt;=$H30),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ30" s="9" t="str">
         <f aca="false">IF(AND(23&gt;=$F30,23&lt;=$H30),1,"")</f>
@@ -5149,41 +5176,41 @@
     </row>
     <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" s="6" t="n">
         <f aca="false">F31+G31-1</f>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>168</v>
+        <v>48</v>
       </c>
       <c r="M31" s="10" t="s">
         <v>61</v>
@@ -5256,33 +5283,33 @@
         <f aca="false">IF(AND(17&gt;=$F31,17&lt;=$H31),1,"")</f>
         <v/>
       </c>
-      <c r="AE31" s="9" t="str">
+      <c r="AE31" s="9" t="n">
         <f aca="false">IF(AND(18&gt;=$F31,18&lt;=$H31),1,"")</f>
-        <v/>
-      </c>
-      <c r="AF31" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="9" t="n">
         <f aca="false">IF(AND(19&gt;=$F31,19&lt;=$H31),1,"")</f>
-        <v/>
-      </c>
-      <c r="AG31" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="9" t="n">
         <f aca="false">IF(AND(20&gt;=$F31,20&lt;=$H31),1,"")</f>
-        <v/>
-      </c>
-      <c r="AH31" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH31" s="9" t="n">
         <f aca="false">IF(AND(21&gt;=$F31,21&lt;=$H31),1,"")</f>
-        <v/>
-      </c>
-      <c r="AI31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" s="9" t="str">
         <f aca="false">IF(AND(22&gt;=$F31,22&lt;=$H31),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AJ31" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AJ31" s="9" t="str">
         <f aca="false">IF(AND(23&gt;=$F31,23&lt;=$H31),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AK31" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AK31" s="9" t="str">
         <f aca="false">IF(AND(24&gt;=$F31,24&lt;=$H31),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL31" s="9" t="str">
         <f aca="false">IF(AND(25&gt;=$F31,25&lt;=$H31),1,"")</f>
@@ -5293,46 +5320,46 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>48</v>
+        <v>157</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H32" s="6" t="n">
         <f aca="false">F32+G32-1</f>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>46</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="M32" s="8" t="s">
-        <v>49</v>
+      <c r="M32" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="N32" s="9" t="str">
         <f aca="false">IF(AND(1&gt;=$F32,1&lt;=$H32),1,"")</f>
@@ -5346,37 +5373,37 @@
         <f aca="false">IF(AND(3&gt;=$F32,3&lt;=$H32),1,"")</f>
         <v/>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="9" t="str">
         <f aca="false">IF(AND(4&gt;=$F32,4&lt;=$H32),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="R32" s="9" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="9" t="str">
         <f aca="false">IF(AND(5&gt;=$F32,5&lt;=$H32),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="S32" s="9" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="9" t="str">
         <f aca="false">IF(AND(6&gt;=$F32,6&lt;=$H32),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="T32" s="9" t="n">
+        <v/>
+      </c>
+      <c r="T32" s="9" t="str">
         <f aca="false">IF(AND(7&gt;=$F32,7&lt;=$H32),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="U32" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="9" t="str">
         <f aca="false">IF(AND(8&gt;=$F32,8&lt;=$H32),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="V32" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="9" t="str">
         <f aca="false">IF(AND(9&gt;=$F32,9&lt;=$H32),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="W32" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="9" t="str">
         <f aca="false">IF(AND(10&gt;=$F32,10&lt;=$H32),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="X32" s="9" t="n">
+        <v/>
+      </c>
+      <c r="X32" s="9" t="str">
         <f aca="false">IF(AND(11&gt;=$F32,11&lt;=$H32),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Y32" s="9" t="str">
         <f aca="false">IF(AND(12&gt;=$F32,12&lt;=$H32),1,"")</f>
@@ -5410,17 +5437,17 @@
         <f aca="false">IF(AND(19&gt;=$F32,19&lt;=$H32),1,"")</f>
         <v/>
       </c>
-      <c r="AG32" s="9" t="str">
+      <c r="AG32" s="9" t="n">
         <f aca="false">IF(AND(20&gt;=$F32,20&lt;=$H32),1,"")</f>
-        <v/>
-      </c>
-      <c r="AH32" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH32" s="9" t="n">
         <f aca="false">IF(AND(21&gt;=$F32,21&lt;=$H32),1,"")</f>
-        <v/>
-      </c>
-      <c r="AI32" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AI32" s="9" t="n">
         <f aca="false">IF(AND(22&gt;=$F32,22&lt;=$H32),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AJ32" s="9" t="str">
         <f aca="false">IF(AND(23&gt;=$F32,23&lt;=$H32),1,"")</f>
@@ -5439,37 +5466,37 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H33" s="6" t="n">
         <f aca="false">F33+G33-1</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>176</v>
@@ -5548,21 +5575,21 @@
         <f aca="false">IF(AND(17&gt;=$F33,17&lt;=$H33),1,"")</f>
         <v/>
       </c>
-      <c r="AE33" s="9" t="n">
+      <c r="AE33" s="9" t="str">
         <f aca="false">IF(AND(18&gt;=$F33,18&lt;=$H33),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AF33" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AF33" s="9" t="str">
         <f aca="false">IF(AND(19&gt;=$F33,19&lt;=$H33),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AG33" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AG33" s="9" t="str">
         <f aca="false">IF(AND(20&gt;=$F33,20&lt;=$H33),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AH33" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AH33" s="9" t="str">
         <f aca="false">IF(AND(21&gt;=$F33,21&lt;=$H33),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AI33" s="9" t="n">
         <f aca="false">IF(AND(22&gt;=$F33,22&lt;=$H33),1,"")</f>
@@ -5572,9 +5599,9 @@
         <f aca="false">IF(AND(23&gt;=$F33,23&lt;=$H33),1,"")</f>
         <v>1</v>
       </c>
-      <c r="AK33" s="9" t="str">
+      <c r="AK33" s="9" t="n">
         <f aca="false">IF(AND(24&gt;=$F33,24&lt;=$H33),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AL33" s="9" t="str">
         <f aca="false">IF(AND(25&gt;=$F33,25&lt;=$H33),1,"")</f>
@@ -5590,41 +5617,41 @@
         <v>178</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H34" s="6" t="n">
         <f aca="false">F34+G34-1</f>
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="M34" s="10" t="s">
-        <v>61</v>
+        <v>48</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="N34" s="9" t="str">
         <f aca="false">IF(AND(1&gt;=$F34,1&lt;=$H34),1,"")</f>
@@ -5638,37 +5665,37 @@
         <f aca="false">IF(AND(3&gt;=$F34,3&lt;=$H34),1,"")</f>
         <v/>
       </c>
-      <c r="Q34" s="9" t="str">
+      <c r="Q34" s="9" t="n">
         <f aca="false">IF(AND(4&gt;=$F34,4&lt;=$H34),1,"")</f>
-        <v/>
-      </c>
-      <c r="R34" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="R34" s="9" t="n">
         <f aca="false">IF(AND(5&gt;=$F34,5&lt;=$H34),1,"")</f>
-        <v/>
-      </c>
-      <c r="S34" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="S34" s="9" t="n">
         <f aca="false">IF(AND(6&gt;=$F34,6&lt;=$H34),1,"")</f>
-        <v/>
-      </c>
-      <c r="T34" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="T34" s="9" t="n">
         <f aca="false">IF(AND(7&gt;=$F34,7&lt;=$H34),1,"")</f>
-        <v/>
-      </c>
-      <c r="U34" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="U34" s="9" t="n">
         <f aca="false">IF(AND(8&gt;=$F34,8&lt;=$H34),1,"")</f>
-        <v/>
-      </c>
-      <c r="V34" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="V34" s="9" t="n">
         <f aca="false">IF(AND(9&gt;=$F34,9&lt;=$H34),1,"")</f>
-        <v/>
-      </c>
-      <c r="W34" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="W34" s="9" t="n">
         <f aca="false">IF(AND(10&gt;=$F34,10&lt;=$H34),1,"")</f>
-        <v/>
-      </c>
-      <c r="X34" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="X34" s="9" t="n">
         <f aca="false">IF(AND(11&gt;=$F34,11&lt;=$H34),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y34" s="9" t="str">
         <f aca="false">IF(AND(12&gt;=$F34,12&lt;=$H34),1,"")</f>
@@ -5686,29 +5713,29 @@
         <f aca="false">IF(AND(15&gt;=$F34,15&lt;=$H34),1,"")</f>
         <v/>
       </c>
-      <c r="AC34" s="9" t="n">
+      <c r="AC34" s="9" t="str">
         <f aca="false">IF(AND(16&gt;=$F34,16&lt;=$H34),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AD34" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AD34" s="9" t="str">
         <f aca="false">IF(AND(17&gt;=$F34,17&lt;=$H34),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AE34" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AE34" s="9" t="str">
         <f aca="false">IF(AND(18&gt;=$F34,18&lt;=$H34),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AF34" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AF34" s="9" t="str">
         <f aca="false">IF(AND(19&gt;=$F34,19&lt;=$H34),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AG34" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AG34" s="9" t="str">
         <f aca="false">IF(AND(20&gt;=$F34,20&lt;=$H34),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AH34" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AH34" s="9" t="str">
         <f aca="false">IF(AND(21&gt;=$F34,21&lt;=$H34),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AI34" s="9" t="str">
         <f aca="false">IF(AND(22&gt;=$F34,22&lt;=$H34),1,"")</f>
@@ -5731,12 +5758,12 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
         <v>182</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>183</v>
@@ -5748,14 +5775,14 @@
         <v>184</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H35" s="6" t="n">
         <f aca="false">F35+G35-1</f>
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>0</v>
@@ -5769,8 +5796,8 @@
       <c r="L35" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="M35" s="8" t="s">
-        <v>49</v>
+      <c r="M35" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="N35" s="9" t="str">
         <f aca="false">IF(AND(1&gt;=$F35,1&lt;=$H35),1,"")</f>
@@ -5784,37 +5811,37 @@
         <f aca="false">IF(AND(3&gt;=$F35,3&lt;=$H35),1,"")</f>
         <v/>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="9" t="str">
         <f aca="false">IF(AND(4&gt;=$F35,4&lt;=$H35),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="R35" s="9" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="9" t="str">
         <f aca="false">IF(AND(5&gt;=$F35,5&lt;=$H35),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="S35" s="9" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="9" t="str">
         <f aca="false">IF(AND(6&gt;=$F35,6&lt;=$H35),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="T35" s="9" t="n">
+        <v/>
+      </c>
+      <c r="T35" s="9" t="str">
         <f aca="false">IF(AND(7&gt;=$F35,7&lt;=$H35),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="U35" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="9" t="str">
         <f aca="false">IF(AND(8&gt;=$F35,8&lt;=$H35),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="V35" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="9" t="str">
         <f aca="false">IF(AND(9&gt;=$F35,9&lt;=$H35),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="W35" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="9" t="str">
         <f aca="false">IF(AND(10&gt;=$F35,10&lt;=$H35),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="X35" s="9" t="n">
+        <v/>
+      </c>
+      <c r="X35" s="9" t="str">
         <f aca="false">IF(AND(11&gt;=$F35,11&lt;=$H35),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Y35" s="9" t="str">
         <f aca="false">IF(AND(12&gt;=$F35,12&lt;=$H35),1,"")</f>
@@ -5840,29 +5867,29 @@
         <f aca="false">IF(AND(17&gt;=$F35,17&lt;=$H35),1,"")</f>
         <v/>
       </c>
-      <c r="AE35" s="9" t="str">
+      <c r="AE35" s="9" t="n">
         <f aca="false">IF(AND(18&gt;=$F35,18&lt;=$H35),1,"")</f>
-        <v/>
-      </c>
-      <c r="AF35" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AF35" s="9" t="n">
         <f aca="false">IF(AND(19&gt;=$F35,19&lt;=$H35),1,"")</f>
-        <v/>
-      </c>
-      <c r="AG35" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AG35" s="9" t="n">
         <f aca="false">IF(AND(20&gt;=$F35,20&lt;=$H35),1,"")</f>
-        <v/>
-      </c>
-      <c r="AH35" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH35" s="9" t="n">
         <f aca="false">IF(AND(21&gt;=$F35,21&lt;=$H35),1,"")</f>
-        <v/>
-      </c>
-      <c r="AI35" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AI35" s="9" t="n">
         <f aca="false">IF(AND(22&gt;=$F35,22&lt;=$H35),1,"")</f>
-        <v/>
-      </c>
-      <c r="AJ35" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AJ35" s="9" t="n">
         <f aca="false">IF(AND(23&gt;=$F35,23&lt;=$H35),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AK35" s="9" t="str">
         <f aca="false">IF(AND(24&gt;=$F35,24&lt;=$H35),1,"")</f>
@@ -5882,26 +5909,26 @@
         <v>187</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>189</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H36" s="6" t="n">
         <f aca="false">F36+G36-1</f>
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I36" s="7" t="n">
         <v>0</v>
@@ -5910,10 +5937,10 @@
         <v>52</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M36" s="10" t="s">
         <v>61</v>
@@ -5978,29 +6005,29 @@
         <f aca="false">IF(AND(15&gt;=$F36,15&lt;=$H36),1,"")</f>
         <v/>
       </c>
-      <c r="AC36" s="9" t="str">
+      <c r="AC36" s="9" t="n">
         <f aca="false">IF(AND(16&gt;=$F36,16&lt;=$H36),1,"")</f>
-        <v/>
-      </c>
-      <c r="AD36" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AD36" s="9" t="n">
         <f aca="false">IF(AND(17&gt;=$F36,17&lt;=$H36),1,"")</f>
-        <v/>
-      </c>
-      <c r="AE36" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AE36" s="9" t="n">
         <f aca="false">IF(AND(18&gt;=$F36,18&lt;=$H36),1,"")</f>
-        <v/>
-      </c>
-      <c r="AF36" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AF36" s="9" t="n">
         <f aca="false">IF(AND(19&gt;=$F36,19&lt;=$H36),1,"")</f>
-        <v/>
-      </c>
-      <c r="AG36" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AG36" s="9" t="n">
         <f aca="false">IF(AND(20&gt;=$F36,20&lt;=$H36),1,"")</f>
-        <v/>
-      </c>
-      <c r="AH36" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH36" s="9" t="n">
         <f aca="false">IF(AND(21&gt;=$F36,21&lt;=$H36),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AI36" s="9" t="str">
         <f aca="false">IF(AND(22&gt;=$F36,22&lt;=$H36),1,"")</f>
@@ -6010,13 +6037,13 @@
         <f aca="false">IF(AND(23&gt;=$F36,23&lt;=$H36),1,"")</f>
         <v/>
       </c>
-      <c r="AK36" s="9" t="n">
+      <c r="AK36" s="9" t="str">
         <f aca="false">IF(AND(24&gt;=$F36,24&lt;=$H36),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="AL36" s="9" t="n">
+        <v/>
+      </c>
+      <c r="AL36" s="9" t="str">
         <f aca="false">IF(AND(25&gt;=$F36,25&lt;=$H36),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AM36" s="9" t="str">
         <f aca="false">IF(AND(26&gt;=$F36,26&lt;=$H36),1,"")</f>
@@ -6025,44 +6052,44 @@
     </row>
     <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>187</v>
-      </c>
       <c r="F37" s="5" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H37" s="6" t="n">
         <f aca="false">F37+G37-1</f>
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I37" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>61</v>
+        <v>195</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="N37" s="9" t="str">
         <f aca="false">IF(AND(1&gt;=$F37,1&lt;=$H37),1,"")</f>
@@ -6076,37 +6103,37 @@
         <f aca="false">IF(AND(3&gt;=$F37,3&lt;=$H37),1,"")</f>
         <v/>
       </c>
-      <c r="Q37" s="9" t="str">
+      <c r="Q37" s="9" t="n">
         <f aca="false">IF(AND(4&gt;=$F37,4&lt;=$H37),1,"")</f>
-        <v/>
-      </c>
-      <c r="R37" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="R37" s="9" t="n">
         <f aca="false">IF(AND(5&gt;=$F37,5&lt;=$H37),1,"")</f>
-        <v/>
-      </c>
-      <c r="S37" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="S37" s="9" t="n">
         <f aca="false">IF(AND(6&gt;=$F37,6&lt;=$H37),1,"")</f>
-        <v/>
-      </c>
-      <c r="T37" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="T37" s="9" t="n">
         <f aca="false">IF(AND(7&gt;=$F37,7&lt;=$H37),1,"")</f>
-        <v/>
-      </c>
-      <c r="U37" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="U37" s="9" t="n">
         <f aca="false">IF(AND(8&gt;=$F37,8&lt;=$H37),1,"")</f>
-        <v/>
-      </c>
-      <c r="V37" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="V37" s="9" t="n">
         <f aca="false">IF(AND(9&gt;=$F37,9&lt;=$H37),1,"")</f>
-        <v/>
-      </c>
-      <c r="W37" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="W37" s="9" t="n">
         <f aca="false">IF(AND(10&gt;=$F37,10&lt;=$H37),1,"")</f>
-        <v/>
-      </c>
-      <c r="X37" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="X37" s="9" t="n">
         <f aca="false">IF(AND(11&gt;=$F37,11&lt;=$H37),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y37" s="9" t="str">
         <f aca="false">IF(AND(12&gt;=$F37,12&lt;=$H37),1,"")</f>
@@ -6164,22 +6191,314 @@
         <f aca="false">IF(AND(25&gt;=$F37,25&lt;=$H37),1,"")</f>
         <v/>
       </c>
-      <c r="AM37" s="9" t="n">
+      <c r="AM37" s="9" t="str">
         <f aca="false">IF(AND(26&gt;=$F37,26&lt;=$H37),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H39" s="11" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="I39" s="12" t="n">
-        <f aca="false">SUM(I5:I37)</f>
+      <c r="C38" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <f aca="false">F38+G38-1</f>
+        <v>25</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="M38" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N38" s="9" t="str">
+        <f aca="false">IF(AND(1&gt;=$F38,1&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="O38" s="9" t="str">
+        <f aca="false">IF(AND(2&gt;=$F38,2&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="P38" s="9" t="str">
+        <f aca="false">IF(AND(3&gt;=$F38,3&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="Q38" s="9" t="str">
+        <f aca="false">IF(AND(4&gt;=$F38,4&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="R38" s="9" t="str">
+        <f aca="false">IF(AND(5&gt;=$F38,5&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="S38" s="9" t="str">
+        <f aca="false">IF(AND(6&gt;=$F38,6&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="T38" s="9" t="str">
+        <f aca="false">IF(AND(7&gt;=$F38,7&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="U38" s="9" t="str">
+        <f aca="false">IF(AND(8&gt;=$F38,8&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="V38" s="9" t="str">
+        <f aca="false">IF(AND(9&gt;=$F38,9&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="W38" s="9" t="str">
+        <f aca="false">IF(AND(10&gt;=$F38,10&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="X38" s="9" t="str">
+        <f aca="false">IF(AND(11&gt;=$F38,11&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="Y38" s="9" t="str">
+        <f aca="false">IF(AND(12&gt;=$F38,12&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="Z38" s="9" t="str">
+        <f aca="false">IF(AND(13&gt;=$F38,13&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="AA38" s="9" t="str">
+        <f aca="false">IF(AND(14&gt;=$F38,14&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="AB38" s="9" t="str">
+        <f aca="false">IF(AND(15&gt;=$F38,15&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="AC38" s="9" t="str">
+        <f aca="false">IF(AND(16&gt;=$F38,16&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="AD38" s="9" t="str">
+        <f aca="false">IF(AND(17&gt;=$F38,17&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="AE38" s="9" t="str">
+        <f aca="false">IF(AND(18&gt;=$F38,18&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="AF38" s="9" t="str">
+        <f aca="false">IF(AND(19&gt;=$F38,19&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="AG38" s="9" t="str">
+        <f aca="false">IF(AND(20&gt;=$F38,20&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="AH38" s="9" t="str">
+        <f aca="false">IF(AND(21&gt;=$F38,21&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="AI38" s="9" t="str">
+        <f aca="false">IF(AND(22&gt;=$F38,22&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ38" s="9" t="str">
+        <f aca="false">IF(AND(23&gt;=$F38,23&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+      <c r="AK38" s="9" t="n">
+        <f aca="false">IF(AND(24&gt;=$F38,24&lt;=$H38),1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="AL38" s="9" t="n">
+        <f aca="false">IF(AND(25&gt;=$F38,25&lt;=$H38),1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="AM38" s="9" t="str">
+        <f aca="false">IF(AND(26&gt;=$F38,26&lt;=$H38),1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <f aca="false">F39+G39-1</f>
+        <v>26</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M39" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N39" s="9" t="str">
+        <f aca="false">IF(AND(1&gt;=$F39,1&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="O39" s="9" t="str">
+        <f aca="false">IF(AND(2&gt;=$F39,2&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="P39" s="9" t="str">
+        <f aca="false">IF(AND(3&gt;=$F39,3&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="Q39" s="9" t="str">
+        <f aca="false">IF(AND(4&gt;=$F39,4&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="R39" s="9" t="str">
+        <f aca="false">IF(AND(5&gt;=$F39,5&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="S39" s="9" t="str">
+        <f aca="false">IF(AND(6&gt;=$F39,6&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="T39" s="9" t="str">
+        <f aca="false">IF(AND(7&gt;=$F39,7&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="U39" s="9" t="str">
+        <f aca="false">IF(AND(8&gt;=$F39,8&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="V39" s="9" t="str">
+        <f aca="false">IF(AND(9&gt;=$F39,9&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="W39" s="9" t="str">
+        <f aca="false">IF(AND(10&gt;=$F39,10&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="X39" s="9" t="str">
+        <f aca="false">IF(AND(11&gt;=$F39,11&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="Y39" s="9" t="str">
+        <f aca="false">IF(AND(12&gt;=$F39,12&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="Z39" s="9" t="str">
+        <f aca="false">IF(AND(13&gt;=$F39,13&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="AA39" s="9" t="str">
+        <f aca="false">IF(AND(14&gt;=$F39,14&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="AB39" s="9" t="str">
+        <f aca="false">IF(AND(15&gt;=$F39,15&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="AC39" s="9" t="str">
+        <f aca="false">IF(AND(16&gt;=$F39,16&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="AD39" s="9" t="str">
+        <f aca="false">IF(AND(17&gt;=$F39,17&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="AE39" s="9" t="str">
+        <f aca="false">IF(AND(18&gt;=$F39,18&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="AF39" s="9" t="str">
+        <f aca="false">IF(AND(19&gt;=$F39,19&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="AG39" s="9" t="str">
+        <f aca="false">IF(AND(20&gt;=$F39,20&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="AH39" s="9" t="str">
+        <f aca="false">IF(AND(21&gt;=$F39,21&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="AI39" s="9" t="str">
+        <f aca="false">IF(AND(22&gt;=$F39,22&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ39" s="9" t="str">
+        <f aca="false">IF(AND(23&gt;=$F39,23&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="AK39" s="9" t="str">
+        <f aca="false">IF(AND(24&gt;=$F39,24&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="AL39" s="9" t="str">
+        <f aca="false">IF(AND(25&gt;=$F39,25&lt;=$H39),1,"")</f>
+        <v/>
+      </c>
+      <c r="AM39" s="9" t="n">
+        <f aca="false">IF(AND(26&gt;=$F39,26&lt;=$H39),1,"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H41" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <f aca="false">SUM(I5:I39)</f>
         <v>24100</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="N5:AM37">
+  <conditionalFormatting sqref="N5:AM39">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>1</formula>
     </cfRule>
@@ -6208,128 +6527,128 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B5" s="13" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="n">
-        <f aca="false">COUNTIF('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B5)</f>
-        <v>6</v>
+        <f aca="false">COUNTIF('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B5)</f>
+        <v>7</v>
       </c>
       <c r="D5" s="14" t="n">
-        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B5,'Plan 180 días'!$M$5:$M$37,"Ejecutable*")</f>
-        <v>6</v>
+        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B5,'Plan 180 días'!$M$5:$M$39,"Ejecutable*")</f>
+        <v>7</v>
       </c>
       <c r="E5" s="14" t="n">
-        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B5,'Plan 180 días'!$M$5:$M$37,"Bloq*")</f>
+        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B5,'Plan 180 días'!$M$5:$M$39,"Bloq*")</f>
         <v>0</v>
       </c>
       <c r="F5" s="12" t="n">
-        <f aca="false">SUMIF('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B5,'Plan 180 días'!$I$5:$I$37)</f>
+        <f aca="false">SUMIF('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B5,'Plan 180 días'!$I$5:$I$39)</f>
         <v>2000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>9</v>
       </c>
       <c r="C6" s="14" t="n">
-        <f aca="false">COUNTIF('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B6)</f>
-        <v>13</v>
+        <f aca="false">COUNTIF('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B6)</f>
+        <v>15</v>
       </c>
       <c r="D6" s="14" t="n">
-        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B6,'Plan 180 días'!$M$5:$M$37,"Ejecutable*")</f>
-        <v>10</v>
+        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B6,'Plan 180 días'!$M$5:$M$39,"Ejecutable*")</f>
+        <v>12</v>
       </c>
       <c r="E6" s="14" t="n">
-        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B6,'Plan 180 días'!$M$5:$M$37,"Bloq*")</f>
+        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B6,'Plan 180 días'!$M$5:$M$39,"Bloq*")</f>
         <v>3</v>
       </c>
       <c r="F6" s="12" t="n">
-        <f aca="false">SUMIF('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B6,'Plan 180 días'!$I$5:$I$37)</f>
+        <f aca="false">SUMIF('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B6,'Plan 180 días'!$I$5:$I$39)</f>
         <v>10000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>13</v>
       </c>
       <c r="C7" s="14" t="n">
-        <f aca="false">COUNTIF('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B7)</f>
-        <v>19</v>
+        <f aca="false">COUNTIF('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B7)</f>
+        <v>21</v>
       </c>
       <c r="D7" s="14" t="n">
-        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B7,'Plan 180 días'!$M$5:$M$37,"Ejecutable*")</f>
-        <v>13</v>
+        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B7,'Plan 180 días'!$M$5:$M$39,"Ejecutable*")</f>
+        <v>15</v>
       </c>
       <c r="E7" s="14" t="n">
-        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B7,'Plan 180 días'!$M$5:$M$37,"Bloq*")</f>
+        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B7,'Plan 180 días'!$M$5:$M$39,"Bloq*")</f>
         <v>6</v>
       </c>
       <c r="F7" s="12" t="n">
-        <f aca="false">SUMIF('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B7,'Plan 180 días'!$I$5:$I$37)</f>
+        <f aca="false">SUMIF('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B7,'Plan 180 días'!$I$5:$I$39)</f>
         <v>15100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>26</v>
       </c>
       <c r="C8" s="14" t="n">
-        <f aca="false">COUNTIF('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B8)</f>
-        <v>33</v>
+        <f aca="false">COUNTIF('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B8)</f>
+        <v>35</v>
       </c>
       <c r="D8" s="14" t="n">
-        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B8,'Plan 180 días'!$M$5:$M$37,"Ejecutable*")</f>
-        <v>13</v>
+        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B8,'Plan 180 días'!$M$5:$M$39,"Ejecutable*")</f>
+        <v>15</v>
       </c>
       <c r="E8" s="14" t="n">
-        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B8,'Plan 180 días'!$M$5:$M$37,"Bloq*")</f>
+        <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B8,'Plan 180 días'!$M$5:$M$39,"Bloq*")</f>
         <v>20</v>
       </c>
       <c r="F8" s="12" t="n">
-        <f aca="false">SUMIF('Plan 180 días'!$H$5:$H$37,"&lt;="&amp;B8,'Plan 180 días'!$I$5:$I$37)</f>
+        <f aca="false">SUMIF('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B8,'Plan 180 días'!$I$5:$I$39)</f>
         <v>24100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -6339,42 +6658,42 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/180-Day Execution Plan.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/180-Day Execution Plan.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="230">
   <si>
     <t xml:space="preserve">Plan de ejecución de 180 días (26 semanas) — Proyecto A con vía B3 en validación</t>
   </si>
@@ -452,16 +452,22 @@
     <t xml:space="preserve">2.5</t>
   </si>
   <si>
-    <t xml:space="preserve">Artes finales de anilla, caja y colofón con advertencias sanitarias</t>
+    <t xml:space="preserve">Diseño profesional (Ruta A v2 con la firma real) y artes finales de anilla, caja y colofón con advertencias sanitarias; encargo de 4.000–15.000 €, se presupuesta el mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Diseñador</t>
   </si>
   <si>
+    <t xml:space="preserve">0.8, 2.1, 2.6</t>
+  </si>
+  <si>
     <t xml:space="preserve">Artes aprobadas por asesor regulatorio</t>
   </si>
   <si>
     <t xml:space="preserve">Conformidad RD 579/2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloqueada (tras el Go de la Fase 0)</t>
   </si>
   <si>
     <t xml:space="preserve">3.1</t>
@@ -4298,7 +4304,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>142</v>
       </c>
@@ -4312,32 +4318,32 @@
         <v>144</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H25" s="6" t="n">
         <f aca="false">F25+G25-1</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>131</v>
+        <v>147</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>148</v>
       </c>
       <c r="N25" s="9" t="str">
         <f aca="false">IF(AND(1&gt;=$F25,1&lt;=$H25),1,"")</f>
@@ -4375,13 +4381,13 @@
         <f aca="false">IF(AND(9&gt;=$F25,9&lt;=$H25),1,"")</f>
         <v/>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="9" t="str">
         <f aca="false">IF(AND(10&gt;=$F25,10&lt;=$H25),1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="X25" s="9" t="n">
+        <v/>
+      </c>
+      <c r="X25" s="9" t="str">
         <f aca="false">IF(AND(11&gt;=$F25,11&lt;=$H25),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Y25" s="9" t="n">
         <f aca="false">IF(AND(12&gt;=$F25,12&lt;=$H25),1,"")</f>
@@ -4391,21 +4397,21 @@
         <f aca="false">IF(AND(13&gt;=$F25,13&lt;=$H25),1,"")</f>
         <v>1</v>
       </c>
-      <c r="AA25" s="9" t="str">
+      <c r="AA25" s="9" t="n">
         <f aca="false">IF(AND(14&gt;=$F25,14&lt;=$H25),1,"")</f>
-        <v/>
-      </c>
-      <c r="AB25" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="9" t="n">
         <f aca="false">IF(AND(15&gt;=$F25,15&lt;=$H25),1,"")</f>
-        <v/>
-      </c>
-      <c r="AC25" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="9" t="n">
         <f aca="false">IF(AND(16&gt;=$F25,16&lt;=$H25),1,"")</f>
-        <v/>
-      </c>
-      <c r="AD25" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="9" t="n">
         <f aca="false">IF(AND(17&gt;=$F25,17&lt;=$H25),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AE25" s="9" t="str">
         <f aca="false">IF(AND(18&gt;=$F25,18&lt;=$H25),1,"")</f>
@@ -4446,13 +4452,13 @@
     </row>
     <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>44</v>
@@ -4477,10 +4483,10 @@
         <v>52</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M26" s="10" t="s">
         <v>61</v>
@@ -4592,19 +4598,19 @@
     </row>
     <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>15</v>
@@ -4623,10 +4629,10 @@
         <v>52</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M27" s="10" t="s">
         <v>61</v>
@@ -4738,19 +4744,19 @@
     </row>
     <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D28" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>152</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>19</v>
@@ -4769,7 +4775,7 @@
         <v>52</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>48</v>
@@ -4884,13 +4890,13 @@
     </row>
     <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>103</v>
@@ -4915,7 +4921,7 @@
         <v>104</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>48</v>
@@ -5030,19 +5036,19 @@
     </row>
     <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>103</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>18</v>
@@ -5061,7 +5067,7 @@
         <v>46</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>48</v>
@@ -5176,19 +5182,19 @@
     </row>
     <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>103</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>18</v>
@@ -5207,7 +5213,7 @@
         <v>46</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>48</v>
@@ -5322,19 +5328,19 @@
     </row>
     <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>20</v>
@@ -5353,7 +5359,7 @@
         <v>46</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>48</v>
@@ -5468,19 +5474,19 @@
     </row>
     <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>103</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>22</v>
@@ -5499,10 +5505,10 @@
         <v>104</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M33" s="10" t="s">
         <v>61</v>
@@ -5614,13 +5620,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>44</v>
@@ -5645,7 +5651,7 @@
         <v>46</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L34" s="4" t="s">
         <v>48</v>
@@ -5760,19 +5766,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>18</v>
@@ -5791,10 +5797,10 @@
         <v>46</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M35" s="10" t="s">
         <v>61</v>
@@ -5906,19 +5912,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>16</v>
@@ -5937,10 +5943,10 @@
         <v>52</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M36" s="10" t="s">
         <v>61</v>
@@ -6052,19 +6058,19 @@
     </row>
     <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>4</v>
@@ -6083,10 +6089,10 @@
         <v>46</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M37" s="8" t="s">
         <v>49</v>
@@ -6198,19 +6204,19 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>24</v>
@@ -6229,10 +6235,10 @@
         <v>52</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M38" s="10" t="s">
         <v>61</v>
@@ -6344,19 +6350,19 @@
     </row>
     <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>26</v>
@@ -6375,7 +6381,7 @@
         <v>52</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>48</v>
@@ -6490,11 +6496,11 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H41" s="11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I41" s="12" t="n">
         <f aca="false">SUM(I5:I39)</f>
-        <v>24100</v>
+        <v>25100</v>
       </c>
     </row>
   </sheetData>
@@ -6527,32 +6533,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B5" s="13" t="n">
         <v>4</v>
@@ -6576,7 +6582,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>9</v>
@@ -6600,18 +6606,18 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>13</v>
       </c>
       <c r="C7" s="14" t="n">
         <f aca="false">COUNTIF('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B7)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="14" t="n">
         <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B7,'Plan 180 días'!$M$5:$M$39,"Ejecutable*")</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" s="14" t="n">
         <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B7,'Plan 180 días'!$M$5:$M$39,"Bloq*")</f>
@@ -6619,12 +6625,12 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIF('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B7,'Plan 180 días'!$I$5:$I$39)</f>
-        <v>15100</v>
+        <v>12100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>26</v>
@@ -6635,20 +6641,20 @@
       </c>
       <c r="D8" s="14" t="n">
         <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B8,'Plan 180 días'!$M$5:$M$39,"Ejecutable*")</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" s="14" t="n">
         <f aca="false">COUNTIFS('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B8,'Plan 180 días'!$M$5:$M$39,"Bloq*")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIF('Plan 180 días'!$H$5:$H$39,"&lt;="&amp;B8,'Plan 180 días'!$I$5:$I$39)</f>
-        <v>24100</v>
+        <v>25100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -6658,42 +6664,42 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/180-Day Execution Plan.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/180-Day Execution Plan.xlsx
@@ -392,7 +392,7 @@
     <t xml:space="preserve">2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Encargar informe de registrabilidad ARNALDO (+ apellido y firma) y reservas FOLIO / LUMBRE (EUIPO, OEPM, OCPI)</t>
+    <t xml:space="preserve">Encargar informe de registrabilidad ARNALDO VALLÉS (+ firma; DON VALLES y ARLONDO) y reservas FOLIO / LUMBRE (EUIPO, OEPM, OCPI)</t>
   </si>
   <si>
     <t xml:space="preserve">Agente de marcas</t>
@@ -3720,7 +3720,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
         <v>122</v>
       </c>
